--- a/static/samples/Analee_Bank_Statement_Template.xlsx
+++ b/static/samples/Analee_Bank_Statement_Template.xlsx
@@ -728,14 +728,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 'Upload Data' and 'Bank Statements' pages: use the .xlsx file (CSV is not reliably read there).</t>
+          <t xml:space="preserve">  - Works on all three pages: Upload Data, Bank Statements, and Historical Data.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 'Historical Data' page: .xlsx or .csv both work.</t>
+          <t xml:space="preserve">  - Both .xlsx and .csv are accepted on every page.</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Max file size 40 MB. Allowed types: .xlsx (everywhere), .csv (Historical Data).</t>
+          <t xml:space="preserve">  - Max file size 40 MB. Allowed types: .xlsx and .csv (both work on every upload page).</t>
         </is>
       </c>
     </row>
